--- a/temp.xlsx
+++ b/temp.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,23 +446,375 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://www.crunchyroll.com/es/discover</t>
+          <t>https://www.tecoloco.com.sv</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Sin título</t>
+          <t>ofertas de trabajo, oportunidades de empleo</t>
         </is>
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Tecnología</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Crunchyroll</t>
+          <t>Trabajo en El Salvador Empleo en El Salvador | www.tecoloco.com.sv 0 favoritos Regístrate Inicio candidatos Menú Acceso Empresas Contrate con Nosotros Compañias Destacadas Testimoniales Cancelar ofertas de trabajo, oportunidades de empleo × Todos los rubros laborables Administración Almacenamiento Apoyo de Oficina Banca | Servicios Financieros Call Center Compras Finanzas | Contabilidad | Auditoría Informática | Internet Mantenimiento Mercadeo | Ventas Operaciones | Logística Producción | Ingeniería | Calidad Publicidad | Comunicaciones | Servicios Puestos Profesionales Recursos Humanos Restaurantes Salud Telecomunicaciones Varios Centroamérica Costa Rica El Salvador Guatemala Honduras Nicaragua Panamá República Dominicana Buscar ahora Ofertas destacadas SUPERVISOR DE SERVICIO AL CLIENTE EN RESTAURANTE POLLO REAL San Salvador, El Salvador Ingeniero para proyecto Comunicaciones Globales San Salvador, El Salvador Técnico de enfermería PREMIUM RESTAURANTS San Salvador, El Salvador Ver más</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>https://www.tecoloco.com.sv/myprofile/saved-jobs</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Inicio de sesión para CANDIDATOS</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Tecnología</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bolsa de trabajo y Ofertas de empleo - Ingreso de candidatos - Tecoloco.com 0 favoritos Regístrate Inicio candidatos Menú Acceso Empresas Contrate con Nosotros Compañias Destacadas Testimoniales Cancelar × Todos los rubros laborables Administración Almacenamiento Apoyo de Oficina Banca | Servicios Financieros Call Center Compras Finanzas | Contabilidad | Auditoría Informática | Internet Mantenimiento Mercadeo | Ventas Operaciones | Logística Producción | Ingeniería | Calidad Publicidad | Comunicaciones | Servicios Puestos Profesionales Recursos Humanos Restaurantes Salud Telecomunicaciones Varios Centroamérica Costa Rica El Salvador Guatemala Honduras Nicaragua Panamá República Dominicana Buscar Inicio de sesión para CANDIDATOS ¿No tienes una cuenta aún? Regístrate hoy ¿Olvidaste la contraseña? Acceso Empresas ¿Sin cuenta empresarial? Empiece aquí Environment: www.tecoloco.com.sv, Build Version: V 1.0.1.0, Date Release: 4/4/2017 Conoce más Inicio Búsqueda de Empleos Quienes Somos Mapa </t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>https://www.tecoloco.com.sv/Candidatos/frmAbreCuenta.aspx</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Regístrate Gratis</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Tecnología</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bolsa de trabajo y Ofertas de empleo - Mi cuenta - Tecoloco.com 0 favoritos Regístrate Inicio candidatos Menú Acceso Empresas Contrate con Nosotros Compañias Destacadas Testimoniales Cancelar × Todos los rubros laborables Administración Almacenamiento Apoyo de Oficina Banca | Servicios Financieros Call Center Compras Finanzas | Contabilidad | Auditoría Informática | Internet Mantenimiento Mercadeo | Ventas Operaciones | Logística Producción | Ingeniería | Calidad Publicidad | Comunicaciones | Servicios Puestos Profesionales Recursos Humanos Restaurantes Salud Telecomunicaciones Varios Centroamérica Costa Rica El Salvador Guatemala Honduras Nicaragua Panamá República Dominicana Buscar Regístrate Gratis ¿Ya tienes una cuenta? Haz clic aquí Datos de la cuenta * Campo requerido Correo Electrónico: * Contraseña * Mostrar Recuerda usar un mínimo de 8 caracteres de largo, incluir al menos un caracter en mayúscula, un caracter numérico y un caracter especial (@,$,!,%,*,#,?,&amp;). Datos Generales </t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>https://www.tecoloco.com.sv/login.aspx</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Inicio de sesión para CANDIDATOS</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Tecnología</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bolsa de trabajo y Ofertas de empleo - Ingreso de candidatos - Tecoloco.com 0 favoritos Regístrate Inicio candidatos Menú Acceso Empresas Contrate con Nosotros Compañias Destacadas Testimoniales Cancelar × Todos los rubros laborables Administración Almacenamiento Apoyo de Oficina Banca | Servicios Financieros Call Center Compras Finanzas | Contabilidad | Auditoría Informática | Internet Mantenimiento Mercadeo | Ventas Operaciones | Logística Producción | Ingeniería | Calidad Publicidad | Comunicaciones | Servicios Puestos Profesionales Recursos Humanos Restaurantes Salud Telecomunicaciones Varios Centroamérica Costa Rica El Salvador Guatemala Honduras Nicaragua Panamá República Dominicana Buscar Inicio de sesión para CANDIDATOS ¿No tienes una cuenta aún? Regístrate hoy ¿Olvidaste la contraseña? Acceso Empresas ¿Sin cuenta empresarial? Empiece aquí Environment: www.tecoloco.com.sv, Build Version: V 1.0.1.0, Date Release: 4/4/2017 Conoce más Inicio Búsqueda de Empleos Quienes Somos Mapa </t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>https://www.tecoloco.com.sv/contrate-con-nosotros</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>¿Por qué tecoloco.com.sv?</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Tecnología</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>tecoloco.com.sv  - contrate con nosotros ACCESO EMPRESAS CONTÁCTENOS BENEFICIOS Exponga sus ofertas de trabajo a más de 2.2 millones de visitas de candidatos al mes a nivel regional Más de 1.5 millones de perfiles activos Cuente con un equipo estratégico y una herramienta especializada en la búsqueda de talento Publique ofertas de trabajo y busque candidatos en nuestra base COMPLETE EL SIGUIENTE FORMULARIO PARA PONERNOS EN CONTACTO CON USTED Tengo una oferta de trabajo para publicar Tengo múltiples ofertas de trabajo para publicar Nombre Nombre Empresa Correo Eléctronico Número de Teléfono Continuar ¿Por qué tecoloco.com.sv? Productos y servicios Testimoniales Tips ¿Por qué tecoloco.com.sv? REDUCCIóN DE COSTOS Con nuestra herramienta encuentre al equipo ideal para su empresa, buscando candidatos y publicando ofertas de trabajo. Cuente con un servicio anual y disminuya sus costos en contratación al tener una cobertura completa, publicaciones con 30 días de duración, recepción de aplicac</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>https://www.tecoloco.com.sv/listado/empresas-destacadas.aspx</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>DIRECTORIO DE EMPRESAS DESTACADAS</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Tecnología</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Empresas destacadas en www.tecoloco.com.sv | 0 favoritos Regístrate Inicio candidatos Menú Acceso Empresas Contrate con Nosotros Compañias Destacadas Testimoniales Cancelar × Todos los rubros laborables Administración Almacenamiento Apoyo de Oficina Banca | Servicios Financieros Call Center Compras Finanzas | Contabilidad | Auditoría Informática | Internet Mantenimiento Mercadeo | Ventas Operaciones | Logística Producción | Ingeniería | Calidad Publicidad | Comunicaciones | Servicios Puestos Profesionales Recursos Humanos Restaurantes Salud Telecomunicaciones Varios Centroamérica Costa Rica El Salvador Guatemala Honduras Nicaragua Panamá República Dominicana Buscar DIRECTORIO DE EMPRESAS DESTACADAS Buscar por empresa Ver listado de nombres de todas las empresas Ver listado de nombres de todas las empresas Búsquedas populares Búsquedas populares Pasantía Java Asesor Eléctrico Motorista Temporal Atención Al Cliente Farmacia Seguridad Asistente .Net Proyectos Inglés Auditoría Informática </t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>https://www.tecoloco.com.sv/SetClickAds?idAd=upVXVOPbpqE%3d</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Donde estés...
+oportunidades en la palma de tu mano</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Tecnología</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Estascontratado.com - descarga nuestra app de empleos trabajos Donde estés... oportunidades en la palma de tu mano Una manera más fácil y rápida de encontrar tu trabajo ideal Con nuestra App tendrás acceso a más de 1,000 ofertas de trabajo en Panamá, la facilidad de recibir notificaciones de nuevas ofertas de tu preferencia y poder aplicar a las mismas; todo desde tu dispositivo móvil sin importar donde estés. Con nuestra App tendrás acceso a más de 4,000 ofertas de trabajo en la región, la facilidad de recibir notificaciones de nuevas ofertas de tu preferencia y poder aplicar a las mismas; todo desde tu dispositivo móvil sin importar donde estés. Descarga nuestra app ahora Cientos de trabajos publicados cada día Recibe notificaciones al instante Selecciona tus plazas favoritas Conoce más detalles a través de nuestro video Ver video Â© EstasContratado.com 2017 Todos los Derechos Reservados</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>https://www.tecoloco.com.sv/1082717/jefe-de-meseros.aspx</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>SUPERVISOR DE SERVICIO AL CLIENTE EN RESTAURANTE</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Tecnología</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>POLLO REAL  SUPERVISOR DE SERVICIO AL CLIENTE EN RESTAURANTE | www.tecoloco.com.sv 0 favoritos Regístrate Inicio candidatos Menú Acceso Empresas Contrate con Nosotros Compañias Destacadas Testimoniales Cancelar × Todos los rubros laborables Administración Almacenamiento Apoyo de Oficina Banca | Servicios Financieros Call Center Compras Finanzas | Contabilidad | Auditoría Informática | Internet Mantenimiento Mercadeo | Ventas Operaciones | Logística Producción | Ingeniería | Calidad Publicidad | Comunicaciones | Servicios Puestos Profesionales Recursos Humanos Restaurantes Salud Telecomunicaciones Varios Centroamérica Costa Rica El Salvador Guatemala Honduras Nicaragua Panamá República Dominicana Buscar Regresar a la búsqueda Compartir esta oferta Facebook Twitter Linkedin WhatsApp SUPERVISOR DE SERVICIO AL CLIENTE EN RESTAURANTE POLLO REAL Expira 17/07/2026 San Salvador, El Salvador Agregar a favoritos Agregar a favoritos Compartir esta Oferta Comparte esta oferta Facebook Twitter Link</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>https://www.tecoloco.com.sv/1082935/ingeniero-electrico.aspx</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Ingeniero para proyecto</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Tecnología</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Comunicaciones Globales Ingeniero para proyecto | www.tecoloco.com.sv 0 favoritos Regístrate Inicio candidatos Menú Acceso Empresas Contrate con Nosotros Compañias Destacadas Testimoniales Cancelar × Todos los rubros laborables Administración Almacenamiento Apoyo de Oficina Banca | Servicios Financieros Call Center Compras Finanzas | Contabilidad | Auditoría Informática | Internet Mantenimiento Mercadeo | Ventas Operaciones | Logística Producción | Ingeniería | Calidad Publicidad | Comunicaciones | Servicios Puestos Profesionales Recursos Humanos Restaurantes Salud Telecomunicaciones Varios Centroamérica Costa Rica El Salvador Guatemala Honduras Nicaragua Panamá República Dominicana Buscar Regresar a la búsqueda Compartir esta oferta Facebook Twitter Linkedin WhatsApp Ingeniero para proyecto Comunicaciones Globales Expira 16/07/2026 San Salvador, El Salvador Agregar a favoritos Agregar a favoritos Compartir esta Oferta Comparte esta oferta Facebook Twitter Linkedin WhatsApp Aplicar Det</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>https://www.tecoloco.com.sv/1082662/enfermero-profesional-auxiliar-de-paramedico.aspx</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Técnico de enfermería</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Tecnología</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>PREMIUM RESTAURANTS Técnico de enfermería | www.tecoloco.com.sv 0 favoritos Regístrate Inicio candidatos Menú Acceso Empresas Contrate con Nosotros Compañias Destacadas Testimoniales Cancelar × Todos los rubros laborables Administración Almacenamiento Apoyo de Oficina Banca | Servicios Financieros Call Center Compras Finanzas | Contabilidad | Auditoría Informática | Internet Mantenimiento Mercadeo | Ventas Operaciones | Logística Producción | Ingeniería | Calidad Publicidad | Comunicaciones | Servicios Puestos Profesionales Recursos Humanos Restaurantes Salud Telecomunicaciones Varios Centroamérica Costa Rica El Salvador Guatemala Honduras Nicaragua Panamá República Dominicana Buscar Regresar a la búsqueda Compartir esta oferta Facebook Twitter Linkedin WhatsApp Técnico de enfermería PREMIUM RESTAURANTS Expira 16/07/2026 San Salvador, El Salvador Agregar a favoritos Agregar a favoritos Compartir esta Oferta Comparte esta oferta Facebook Twitter Linkedin WhatsApp Aplicar Detalle de la O</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>https://www.tecoloco.com.sv/empresas-destacadas/trabajos-en-distribuidora-morazan_2208.aspx</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Share this Page</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>408.8</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Tecnología</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Trabajos en DISTRIBUIDORA MORAZÁN en El Salvador . 0 favoritos Regístrate Inicio candidatos Menú Acceso Empresas Contrate con Nosotros Compañias Destacadas Testimoniales Cancelar × Todos los rubros laborables Administración Almacenamiento Apoyo de Oficina Banca | Servicios Financieros Call Center Compras Finanzas | Contabilidad | Auditoría Informática | Internet Mantenimiento Mercadeo | Ventas Operaciones | Logística Producción | Ingeniería | Calidad Publicidad | Comunicaciones | Servicios Puestos Profesionales Recursos Humanos Restaurantes Salud Telecomunicaciones Varios Centroamérica Costa Rica El Salvador Guatemala Honduras Nicaragua Panamá República Dominicana Buscar Perfil Ofertas (23) Share This Page Facebook Twitter Google Plus Email Share This Page Share this Page × Facebook Twitter Google Plus Email DISTRIBUIDORA MORAZÁN Somos una empresa de productos de consumo masivo, la cual tiene como finalidad brindar servicio de distribución y construcción de marcas en El Salvador, con u</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>https://www.tecoloco.com.sv/empresas-destacadas/trabajos-en-impressa-repuestos_2209.aspx</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Share this Page</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Tecnología</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Trabajos en IMPRESSA REPUESTOS en El Salvador . 0 favoritos Regístrate Inicio candidatos Menú Acceso Empresas Contrate con Nosotros Compañias Destacadas Testimoniales Cancelar × Todos los rubros laborables Administración Almacenamiento Apoyo de Oficina Banca | Servicios Financieros Call Center Compras Finanzas | Contabilidad | Auditoría Informática | Internet Mantenimiento Mercadeo | Ventas Operaciones | Logística Producción | Ingeniería | Calidad Publicidad | Comunicaciones | Servicios Puestos Profesionales Recursos Humanos Restaurantes Salud Telecomunicaciones Varios Centroamérica Costa Rica El Salvador Guatemala Honduras Nicaragua Panamá República Dominicana Buscar Perfil Ofertas (33) Share This Page Facebook Twitter Google Plus Email Share This Page Share this Page × Facebook Twitter Google Plus Email IMPRESSA REPUESTOS IMPRESSA comprometida con sus clientes le ofrece los mejores precios, facilidad de horarios y una extensa gama de repuestos con excelente calidad. información Quién</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>https://www.tecoloco.com.sv/empresas-destacadas/trabajos-en-ransa_2429.aspx</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Share this Page</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>408.8</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Tecnología</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Trabajos en RANSA en El Salvador . 0 favoritos Regístrate Inicio candidatos Menú Acceso Empresas Contrate con Nosotros Compañias Destacadas Testimoniales Cancelar × Todos los rubros laborables Administración Almacenamiento Apoyo de Oficina Banca | Servicios Financieros Call Center Compras Finanzas | Contabilidad | Auditoría Informática | Internet Mantenimiento Mercadeo | Ventas Operaciones | Logística Producción | Ingeniería | Calidad Publicidad | Comunicaciones | Servicios Puestos Profesionales Recursos Humanos Restaurantes Salud Telecomunicaciones Varios Centroamérica Costa Rica El Salvador Guatemala Honduras Nicaragua Panamá República Dominicana Buscar Perfil Ofertas (24) Share This Page Facebook Twitter Google Plus Email Share This Page Share this Page × Facebook Twitter Google Plus Email RANSA Ransa es el operador logístico líder de Latinoamérica, opera en 7 países: Perú, Región Andina (Bolivia, Ecuador y Colombia) y Centroamérica (Guatemala, Honduras y El Salvador). Tenemos 80 añ</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>https://www.tecoloco.com.sv/empresas-destacadas/trabajos-en-sarita_3036.aspx</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Share this Page</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>408.8</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Tecnología</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Trabajos en SARITA en El Salvador . 0 favoritos Regístrate Inicio candidatos Menú Acceso Empresas Contrate con Nosotros Compañias Destacadas Testimoniales Cancelar × Todos los rubros laborables Administración Almacenamiento Apoyo de Oficina Banca | Servicios Financieros Call Center Compras Finanzas | Contabilidad | Auditoría Informática | Internet Mantenimiento Mercadeo | Ventas Operaciones | Logística Producción | Ingeniería | Calidad Publicidad | Comunicaciones | Servicios Puestos Profesionales Recursos Humanos Restaurantes Salud Telecomunicaciones Varios Centroamérica Costa Rica El Salvador Guatemala Honduras Nicaragua Panamá República Dominicana Buscar Perfil Ofertas (20) Share This Page Facebook Twitter Google Plus Email Share This Page Share this Page × Facebook Twitter Google Plus Email SARITA En 1948 inicia la historia de Helados Sarita. Surgió como una de las empresas pioneras en la fabricación Comercial del  Helado en Centro América. Somos una empresa que se dedica a la Fabri</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>https://www.tecoloco.com.sv/empresas-destacadas/trabajos-en-concentrix_3158.aspx</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Share this Page</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Tecnología</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Trabajos en CONCENTRIX en El Salvador . 0 favoritos Regístrate Inicio candidatos Menú Acceso Empresas Contrate con Nosotros Compañias Destacadas Testimoniales Cancelar × Todos los rubros laborables Administración Almacenamiento Apoyo de Oficina Banca | Servicios Financieros Call Center Compras Finanzas | Contabilidad | Auditoría Informática | Internet Mantenimiento Mercadeo | Ventas Operaciones | Logística Producción | Ingeniería | Calidad Publicidad | Comunicaciones | Servicios Puestos Profesionales Recursos Humanos Restaurantes Salud Telecomunicaciones Varios Centroamérica Costa Rica El Salvador Guatemala Honduras Nicaragua Panamá República Dominicana Buscar Perfil Ofertas (35) Share This Page Facebook Twitter Google Plus Email Share This Page Share this Page × Facebook Twitter Google Plus Email CONCENTRIX We’re Concentrix. A new breed of tech company — Human-centered. Tech-powered. Intelligence-fueled. We design, build, and run enterprise-wide technology and solutions that touch hea</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>https://www.tecoloco.com.sv/empresas-destacadas/trabajos-en-don-pollo_3194.aspx</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Share this Page</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Tecnología</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Trabajos en DON POLLO en El Salvador . 0 favoritos Regístrate Inicio candidatos Menú Acceso Empresas Contrate con Nosotros Compañias Destacadas Testimoniales Cancelar × Todos los rubros laborables Administración Almacenamiento Apoyo de Oficina Banca | Servicios Financieros Call Center Compras Finanzas | Contabilidad | Auditoría Informática | Internet Mantenimiento Mercadeo | Ventas Operaciones | Logística Producción | Ingeniería | Calidad Publicidad | Comunicaciones | Servicios Puestos Profesionales Recursos Humanos Restaurantes Salud Telecomunicaciones Varios Centroamérica Costa Rica El Salvador Guatemala Honduras Nicaragua Panamá República Dominicana Buscar Perfil Ofertas (29) Share This Page Facebook Twitter Google Plus Email Share This Page Share this Page × Facebook Twitter Google Plus Email DON POLLO Don pollo es parte del portafolio de negocios de CMI - Corporación Multi Inverciones- Con presencia en El Salvador, Don Pollo es una marca que ofrece una opción deliciosa de pollo fr</t>
         </is>
       </c>
     </row>
